--- a/从零开始学Slots/从零开始学Slots-33-数值篇-MegaSymbols(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-33-数值篇-MegaSymbols(1).xlsx
@@ -7449,6 +7449,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N154" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -8133,5 +8136,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Q70" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-33-数值篇-MegaSymbols(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-33-数值篇-MegaSymbols(1).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="169">
   <si>
     <r>
       <rPr>
@@ -6399,7 +6399,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6538,6 +6538,14 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -7019,13 +7027,13 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
+      <c r="A45" s="35">
+        <v>5</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
+      <c r="A46" s="35">
+        <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8053,8 +8061,8 @@
       <c r="H45" s="14"/>
     </row>
     <row r="46" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="17" t="s">
-        <v>162</v>
+      <c r="A46" s="36">
+        <v>6</v>
       </c>
       <c r="B46" s="29" t="str">
         <f aca="false">IF(ABS(B24-1)&lt;0.0001,"✓","✗")</f>
@@ -8065,8 +8073,8 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="17" t="s">
-        <v>164</v>
+      <c r="A47" s="36">
+        <v>4</v>
       </c>
       <c r="B47" s="29" t="str">
         <f aca="false">IF(ABS(H32-1)&lt;0.0001,"✓","✗")</f>

--- a/从零开始学Slots/从零开始学Slots-33-数值篇-MegaSymbols(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-33-数值篇-MegaSymbols(1).xlsx
@@ -6212,10 +6212,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -6399,7 +6400,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6545,6 +6546,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7731,7 +7740,7 @@
       <c r="A24" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="B24" s="23" t="n">
+      <c r="B24" s="38" t="n">
         <f aca="false">SUM(B18:B23)</f>
         <v>1</v>
       </c>
@@ -7799,7 +7808,7 @@
       <c r="G28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="23" t="n">
+      <c r="H28" s="38" t="n">
         <f aca="false">B28*$B$18+C28*$B$19+D28*$B$20+E28*$B$21+F28*$B$22+G28*$B$23</f>
         <v>0.45</v>
       </c>
@@ -7826,7 +7835,7 @@
       <c r="G29" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="23" t="n">
+      <c r="H29" s="38" t="n">
         <f aca="false">B29*$B$18+C29*$B$19+D29*$B$20+E29*$B$21+F29*$B$22+G29*$B$23</f>
         <v>0.3</v>
       </c>
@@ -7853,7 +7862,7 @@
       <c r="G30" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="23" t="n">
+      <c r="H30" s="38" t="n">
         <f aca="false">B30*$B$18+C30*$B$19+D30*$B$20+E30*$B$21+F30*$B$22+G30*$B$23</f>
         <v>0.25</v>
       </c>
@@ -7880,7 +7889,7 @@
       <c r="G31" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="23" t="n">
+      <c r="H31" s="38" t="n">
         <f aca="false">B31*$B$18+C31*$B$19+D31*$B$20+E31*$B$21+F31*$B$22+G31*$B$23</f>
         <v>0</v>
       </c>
@@ -7889,7 +7898,7 @@
       <c r="A32" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="H32" s="23" t="n">
+      <c r="H32" s="38" t="n">
         <f aca="false">SUM(H28:H31)</f>
         <v>1</v>
       </c>
@@ -7944,7 +7953,7 @@
       <c r="A37" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B37" s="23" t="n">
+      <c r="B37" s="38" t="n">
         <f aca="false">H28</f>
         <v>0.45</v>
       </c>
@@ -7960,7 +7969,7 @@
       <c r="A38" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B38" s="23" t="n">
+      <c r="B38" s="38" t="n">
         <f aca="false">H29</f>
         <v>0.3</v>
       </c>
@@ -7976,7 +7985,7 @@
       <c r="A39" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="23" t="n">
+      <c r="B39" s="38" t="n">
         <f aca="false">H30</f>
         <v>0.25</v>
       </c>
@@ -7992,7 +8001,7 @@
       <c r="A40" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B40" s="23" t="n">
+      <c r="B40" s="38" t="n">
         <f aca="false">H31</f>
         <v>0</v>
       </c>
